--- a/BaoCao/BaoCao_CongNo_20260901_20260930.xlsx
+++ b/BaoCao/BaoCao_CongNo_20260901_20260930.xlsx
@@ -21,11 +21,11 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tong_Hop_Tuan'!$1:$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chi_Tiet_Ca_Nhan'!$A$5:$J$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Chi_Tiet_Ca_Nhan'!$1:$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Chi_Tiet_Tien_Com'!$A$5:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Chi_Tiet_Tien_Com'!$A$5:$H$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Chi_Tiet_Tien_Com'!$1:$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Lich_Su_Nop_Tien'!$A$5:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Lich_Su_Nop_Tien'!$A$5:$H$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Lich_Su_Nop_Tien'!$1:$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Van_De_Phat_Sinh'!$A$5:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Van_De_Phat_Sinh'!$A$5:$G$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Van_De_Phat_Sinh'!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -184,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -211,7 +211,7 @@
     <xf numFmtId="164" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -220,10 +220,7 @@
     <xf numFmtId="164" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -658,17 +655,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Phải trả: 150,000</t>
+          <t>Phải trả: 255,000</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Đã nộp: 160,000</t>
+          <t>Đã nộp: 225,000</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Chênh lệch: 10,000</t>
+          <t>Chênh lệch: -30,000</t>
         </is>
       </c>
     </row>
@@ -731,19 +728,19 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Cổ</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29 23:51:45</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="E6" s="8" t="n">
@@ -753,61 +750,61 @@
         <v>60000</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="I6" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>Đã đủ</t>
+          <t>Còn nợ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Test 2</t>
+          <t>Huyền</t>
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>2026-09-29 22:51:07</t>
+          <t>Văn Phòng</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>30000</v>
+        <v>65000</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>100000</v>
+        <v>65000</v>
       </c>
       <c r="H7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>Nộp thừa</t>
+          <t>Đã đủ</t>
         </is>
       </c>
     </row>
@@ -817,7 +814,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Test 3</t>
+          <t>Hưng</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
@@ -825,98 +822,92 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29 23:53:30</t>
+          <t>Kho</t>
         </is>
       </c>
       <c r="E8" s="8" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>30000</v>
+        <v>65000</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>-30000</v>
-      </c>
-      <c r="K8" s="14" t="inlineStr">
-        <is>
-          <t>Còn nợ</t>
+        <v>0</v>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>Đã đủ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Test 4</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-30 04:04:24</t>
-        </is>
-      </c>
+          <t>Lượng</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr"/>
+      <c r="D9" s="11" t="inlineStr"/>
       <c r="E9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="12" t="n">
+        <v>65000</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>65000</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>Đã đủ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="15" t="n">
+        <v>255000</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>225000</v>
+      </c>
+      <c r="H10" s="15" t="n">
         <v>30000</v>
       </c>
-      <c r="G9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>30000</v>
-      </c>
-      <c r="I9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>-30000</v>
-      </c>
-      <c r="K9" s="14" t="inlineStr">
-        <is>
-          <t>Còn nợ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="16" t="n">
-        <v>150000</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>160000</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <v>60000</v>
-      </c>
-      <c r="I10" s="16" t="n">
-        <v>70000</v>
-      </c>
-      <c r="J10" s="15" t="n"/>
-      <c r="K10" s="15" t="n"/>
+      <c r="I10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="14" t="n"/>
+      <c r="K10" s="14" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:K10"/>
@@ -929,7 +920,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CTrang &amp;P / &amp;N&amp;RXuất ngày: 30/09/2026</oddFooter>
+    <oddFooter>&amp;CTrang &amp;P / &amp;N&amp;RXuất ngày: 01/10/2026</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -949,8 +940,8 @@
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -995,17 +986,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Phải trả: 150,000</t>
+          <t>Phải trả: 255,000</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Đã nộp: 160,000</t>
+          <t>Đã nộp: 95,000</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Chênh lệch: 10,000</t>
+          <t>Chênh lệch: -160,000</t>
         </is>
       </c>
     </row>
@@ -1062,10 +1053,10 @@
           <t>Tuần 1</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="16" t="n">
         <v>46265</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="16" t="n">
         <v>46270</v>
       </c>
       <c r="D6" s="8" t="n">
@@ -1083,7 +1074,7 @@
       <c r="H6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Đã đủ</t>
         </is>
@@ -1095,10 +1086,10 @@
           <t>Tuần 2</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="17" t="n">
         <v>46272</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="17" t="n">
         <v>46277</v>
       </c>
       <c r="D7" s="11" t="n">
@@ -1116,7 +1107,7 @@
       <c r="H7" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>Đã đủ</t>
         </is>
@@ -1128,10 +1119,10 @@
           <t>Tuần 3</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="16" t="n">
         <v>46279</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="16" t="n">
         <v>46284</v>
       </c>
       <c r="D8" s="8" t="n">
@@ -1149,7 +1140,7 @@
       <c r="H8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>Đã đủ</t>
         </is>
@@ -1161,30 +1152,30 @@
           <t>Tuần 4</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="17" t="n">
         <v>46286</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="17" t="n">
         <v>46291</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0</v>
+        <v>255000</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>Đã đủ</t>
+          <t>Còn nợ</t>
         </is>
       </c>
     </row>
@@ -1194,55 +1185,55 @@
           <t>Tuần 5</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="16" t="n">
         <v>46293</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="16" t="n">
         <v>46298</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>160000</v>
+        <v>0</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>Nộp thừa</t>
+        <v>0</v>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Còn nợ</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="16" t="n">
-        <v>150000</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>10000</v>
-      </c>
-      <c r="I11" s="15" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="15" t="n">
+        <v>255000</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>95000</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>190000</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="14" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:I11"/>
@@ -1255,7 +1246,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CTrang &amp;P / &amp;N&amp;RXuất ngày: 30/09/2026</oddFooter>
+    <oddFooter>&amp;CTrang &amp;P / &amp;N&amp;RXuất ngày: 01/10/2026</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1275,8 +1266,8 @@
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -1323,17 +1314,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Phải trả: 150,000</t>
+          <t>Phải trả: 255,000</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Đã nộp: 160,000</t>
+          <t>Đã nộp: 225,000</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Chênh lệch: 10,000</t>
+          <t>Chênh lệch: -30,000</t>
         </is>
       </c>
     </row>
@@ -1391,16 +1382,16 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Cổ</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29 23:51:45</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="D6" s="8" t="n">
@@ -1410,58 +1401,58 @@
         <v>60000</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="J6" s="10" t="inlineStr">
         <is>
-          <t>Đã đủ</t>
+          <t>Còn nợ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Test 2</t>
+          <t>Huyền</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>2026-09-29 22:51:07</t>
+          <t>Văn Phòng</t>
         </is>
       </c>
       <c r="D7" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>30000</v>
+        <v>65000</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>100000</v>
+        <v>65000</v>
       </c>
       <c r="G7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="12" t="n">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>70000</v>
+        <v>0</v>
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
-          <t>Nộp thừa</t>
+          <t>Đã đủ</t>
         </is>
       </c>
     </row>
@@ -1471,99 +1462,95 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Test 3</t>
+          <t>Hưng</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29 23:53:30</t>
+          <t>Kho</t>
         </is>
       </c>
       <c r="D8" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>30000</v>
+        <v>65000</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>-30000</v>
-      </c>
-      <c r="J8" s="14" t="inlineStr">
-        <is>
-          <t>Còn nợ</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>Đã đủ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Test 4</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-30 04:04:24</t>
-        </is>
-      </c>
+          <t>Lượng</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr"/>
       <c r="D9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="12" t="n">
+        <v>65000</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>65000</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>Đã đủ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>255000</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>225000</v>
+      </c>
+      <c r="G10" s="15" t="n">
         <v>30000</v>
       </c>
-      <c r="F9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>30000</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>-30000</v>
-      </c>
-      <c r="J9" s="14" t="inlineStr">
-        <is>
-          <t>Còn nợ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="16" t="n">
-        <v>150000</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>60000</v>
-      </c>
-      <c r="H10" s="16" t="n">
-        <v>70000</v>
-      </c>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="n"/>
+      <c r="H10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="14" t="n"/>
+      <c r="J10" s="14" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:J10"/>
@@ -1576,7 +1563,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CTrang &amp;P / &amp;N&amp;RXuất ngày: 30/09/2026</oddFooter>
+    <oddFooter>&amp;CTrang &amp;P / &amp;N&amp;RXuất ngày: 01/10/2026</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1591,16 +1578,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1635,7 +1622,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Số dòng: 7</t>
+          <t>Số dòng: 8</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -1698,21 +1685,21 @@
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Cổ</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29 23:51:45</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
+          <t>CNC</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -1732,21 +1719,21 @@
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Cổ</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>2026-09-29 23:51:45</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
+          <t>CNC</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -1766,21 +1753,21 @@
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Test 2</t>
+          <t>Huyền</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29 22:51:07</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
+          <t>Văn Phòng</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -1789,7 +1776,7 @@
         </is>
       </c>
       <c r="F8" s="9" t="n">
-        <v>30000</v>
+        <v>35000</v>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
@@ -1800,34 +1787,34 @@
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Test 2</t>
+          <t>Huyền</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>2026-09-29 22:51:07</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
+          <t>Văn Phòng</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Không</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="F9" s="12" t="n">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Đăng ký</t>
+          <t>Đã ăn</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr"/>
@@ -1838,17 +1825,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Test 3</t>
+          <t>Hưng</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29 23:53:30</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
+          <t>Kho</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -1857,7 +1844,7 @@
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>30000</v>
+        <v>35000</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -1868,21 +1855,21 @@
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Test 4</t>
+          <t>Hưng</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>2026-09-30 04:04:24</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
+          <t>Kho</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -1901,25 +1888,23 @@
       <c r="H11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr"/>
+      <c r="A12" s="8" t="n">
+        <v>1</v>
+      </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>VinCent</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Laservall</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
+          <t>Lượng</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr"/>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Phát sinh</t>
+          <t>Có</t>
         </is>
       </c>
       <c r="F12" s="9" t="n">
@@ -1927,29 +1912,59 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Suất phát sinh</t>
+          <t>Đã ăn</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr"/>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Lượng</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr"/>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>Đã ăn</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="16" t="n">
-        <v>185000</v>
-      </c>
-      <c r="G13" s="15" t="n"/>
-      <c r="H13" s="15" t="n"/>
+      <c r="B14" s="14" t="n"/>
+      <c r="C14" s="14" t="n"/>
+      <c r="D14" s="14" t="n"/>
+      <c r="E14" s="14" t="n"/>
+      <c r="F14" s="15" t="n">
+        <v>255000</v>
+      </c>
+      <c r="G14" s="14" t="n"/>
+      <c r="H14" s="14" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H13"/>
+  <autoFilter ref="A5:H14"/>
   <mergeCells count="3">
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A2:H2"/>
@@ -1959,7 +1974,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CTrang &amp;P / &amp;N&amp;RXuất ngày: 30/09/2026</oddFooter>
+    <oddFooter>&amp;CTrang &amp;P / &amp;N&amp;RXuất ngày: 01/10/2026</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1974,7 +1989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1983,8 +1998,8 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2018,7 +2033,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Số dòng: 2</t>
+          <t>Số dòng: 4</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -2088,28 +2103,28 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Test 2</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>CNC</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
+          <t>Lượng</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
-        <v>100000</v>
+        <v>65000</v>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Tiền mặt</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>Tiền cơm 21-26/9</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="n">
@@ -2120,47 +2135,123 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Huyền</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
+          <t>Văn Phòng</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>65000</v>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Chuyển khoản</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>Tiền cơm 21-26/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Hưng</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
           <t>Kho</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>60000</v>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>65000</v>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Chuyển khoản</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Tiền cơm 21-26/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Cổ</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>CNC</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Tiền mặt</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Tiền cơm 21-26/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="16" t="n">
-        <v>160000</v>
-      </c>
-      <c r="G8" s="15" t="n"/>
-      <c r="H8" s="15" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="15" t="n">
+        <v>225000</v>
+      </c>
+      <c r="G10" s="14" t="n"/>
+      <c r="H10" s="14" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H8"/>
+  <autoFilter ref="A5:H10"/>
   <mergeCells count="3">
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A2:H2"/>
@@ -2170,7 +2261,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CTrang &amp;P / &amp;N&amp;RXuất ngày: 30/09/2026</oddFooter>
+    <oddFooter>&amp;CTrang &amp;P / &amp;N&amp;RXuất ngày: 01/10/2026</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2185,16 +2276,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -2227,7 +2318,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Số dòng: 4</t>
+          <t>Số dòng: 1</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -2286,142 +2377,53 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Số dư</t>
+          <t>Công nợ</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Test 2</t>
+          <t>Cổ</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-29 22:51:07</t>
+          <t>CNC</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>70000</v>
+        <v>30000</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Người ăn đang có số tiền dư</t>
+          <t>Còn công nợ chưa thanh toán</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Theo dõi kỳ sau</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Công nợ</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>Test 3</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-29 23:53:30</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="n">
+          <t>Cần xử lý</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n"/>
+      <c r="C7" s="14" t="n"/>
+      <c r="D7" s="14" t="n"/>
+      <c r="E7" s="15" t="n">
         <v>30000</v>
       </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>Còn công nợ chưa thanh toán</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>Cần xử lý</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Công nợ</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Test 4</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-30 04:04:24</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>Còn công nợ chưa thanh toán</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>Cần xử lý</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Suất ăn phát sinh</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr"/>
-      <c r="C9" s="11" t="inlineStr"/>
-      <c r="D9" s="11" t="inlineStr"/>
-      <c r="E9" s="12" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>Có suất ăn phát sinh chưa gắn với người ăn</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
-        <is>
-          <t>Cần đối chiếu</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>TỔNG CỘNG</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="16" t="n">
-        <v>165000</v>
-      </c>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+      <c r="F7" s="14" t="n"/>
+      <c r="G7" s="14" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:G10"/>
+  <autoFilter ref="A5:G7"/>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A2:G2"/>
@@ -2431,7 +2433,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;CTrang &amp;P / &amp;N&amp;RXuất ngày: 30/09/2026</oddFooter>
+    <oddFooter>&amp;CTrang &amp;P / &amp;N&amp;RXuất ngày: 01/10/2026</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
